--- a/output/yearly_total_coral_cover_iteration_5_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_5_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.266598300915104</v>
+        <v>1.260442742809476</v>
       </c>
       <c r="C3" t="n">
-        <v>4.615143816096092</v>
+        <v>4.606013562446597</v>
       </c>
       <c r="D3" t="n">
-        <v>6.116695716689532</v>
+        <v>6.103314495480647</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99843783370073</v>
+        <v>11.96977080073672</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.410995200069481</v>
+        <v>1.396676421381979</v>
       </c>
       <c r="C4" t="n">
-        <v>5.077333701897731</v>
+        <v>5.062996492293647</v>
       </c>
       <c r="D4" t="n">
-        <v>6.358745566468012</v>
+        <v>6.342292053805713</v>
       </c>
       <c r="E4" t="n">
-        <v>12.84707446843522</v>
+        <v>12.80196496748134</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.602379317628255</v>
+        <v>1.578802158184034</v>
       </c>
       <c r="C5" t="n">
-        <v>5.626521552715709</v>
+        <v>5.671633752341928</v>
       </c>
       <c r="D5" t="n">
-        <v>6.649290428895637</v>
+        <v>6.71079992001698</v>
       </c>
       <c r="E5" t="n">
-        <v>13.8781912992396</v>
+        <v>13.96123583054294</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.81492625319356</v>
+        <v>1.781290504986722</v>
       </c>
       <c r="C6" t="n">
-        <v>6.255588454374857</v>
+        <v>6.415115917972972</v>
       </c>
       <c r="D6" t="n">
-        <v>6.981987050011323</v>
+        <v>7.054469161458062</v>
       </c>
       <c r="E6" t="n">
-        <v>15.05250175757974</v>
+        <v>15.25087558441776</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.05443378107531</v>
+        <v>2.008456258118875</v>
       </c>
       <c r="C7" t="n">
-        <v>6.95051437761285</v>
+        <v>7.335108062210844</v>
       </c>
       <c r="D7" t="n">
-        <v>7.277528952537383</v>
+        <v>7.43124499778359</v>
       </c>
       <c r="E7" t="n">
-        <v>16.28247711122554</v>
+        <v>16.77480931811331</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.288182296223674</v>
+        <v>1.235536555837691</v>
       </c>
       <c r="C8" t="n">
-        <v>4.487907265516561</v>
+        <v>5.086703622820599</v>
       </c>
       <c r="D8" t="n">
-        <v>5.474135648005301</v>
+        <v>5.713769578140964</v>
       </c>
       <c r="E8" t="n">
-        <v>11.25022520974554</v>
+        <v>12.03600975679925</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.663196804419621</v>
+        <v>1.565974206150838</v>
       </c>
       <c r="C9" t="n">
-        <v>5.358131287929252</v>
+        <v>6.338152495282044</v>
       </c>
       <c r="D9" t="n">
-        <v>5.88399668607881</v>
+        <v>6.185634878927182</v>
       </c>
       <c r="E9" t="n">
-        <v>12.90532477842768</v>
+        <v>14.08976158036006</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.0712450464684</v>
+        <v>1.915029934781693</v>
       </c>
       <c r="C10" t="n">
-        <v>6.372134712240671</v>
+        <v>7.798082897987398</v>
       </c>
       <c r="D10" t="n">
-        <v>6.38912852937855</v>
+        <v>6.656282297671239</v>
       </c>
       <c r="E10" t="n">
-        <v>14.83250828808762</v>
+        <v>16.36939513044033</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.502003766457835</v>
+        <v>2.261715931167918</v>
       </c>
       <c r="C11" t="n">
-        <v>7.478507415542716</v>
+        <v>9.377269120524863</v>
       </c>
       <c r="D11" t="n">
-        <v>6.87179349107999</v>
+        <v>7.106183716762858</v>
       </c>
       <c r="E11" t="n">
-        <v>16.85230467308054</v>
+        <v>18.74516876845564</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.945196355465004</v>
+        <v>2.612005334209512</v>
       </c>
       <c r="C12" t="n">
-        <v>8.718475722688105</v>
+        <v>11.02054820044896</v>
       </c>
       <c r="D12" t="n">
-        <v>7.436550331504492</v>
+        <v>7.556019716006806</v>
       </c>
       <c r="E12" t="n">
-        <v>19.1002224096576</v>
+        <v>21.18857325066528</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.41169279496063</v>
+        <v>2.943727208531993</v>
       </c>
       <c r="C13" t="n">
-        <v>10.01687434794491</v>
+        <v>12.69204295887494</v>
       </c>
       <c r="D13" t="n">
-        <v>8.088911306207599</v>
+        <v>8.00301768980259</v>
       </c>
       <c r="E13" t="n">
-        <v>21.51747844911314</v>
+        <v>23.63878785720952</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.970966508522939</v>
+        <v>1.688399884286622</v>
       </c>
       <c r="C14" t="n">
-        <v>7.170518334708981</v>
+        <v>8.787015017136568</v>
       </c>
       <c r="D14" t="n">
-        <v>6.188230669224835</v>
+        <v>6.048174541736985</v>
       </c>
       <c r="E14" t="n">
-        <v>15.32971551245675</v>
+        <v>16.52358944316017</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.078418794752752</v>
+        <v>1.732401816390964</v>
       </c>
       <c r="C15" t="n">
-        <v>7.663660024029197</v>
+        <v>9.53579399116561</v>
       </c>
       <c r="D15" t="n">
-        <v>6.273142028165141</v>
+        <v>6.043471970233643</v>
       </c>
       <c r="E15" t="n">
-        <v>16.01522084694709</v>
+        <v>17.31166777779022</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.476016797495668</v>
+        <v>2.014477566775157</v>
       </c>
       <c r="C16" t="n">
-        <v>9.038813668321788</v>
+        <v>11.28315764256929</v>
       </c>
       <c r="D16" t="n">
-        <v>6.799054455853115</v>
+        <v>6.535170490428616</v>
       </c>
       <c r="E16" t="n">
-        <v>18.31388492167057</v>
+        <v>19.83280569977307</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.032374827423577</v>
+        <v>1.619265210953562</v>
       </c>
       <c r="C17" t="n">
-        <v>8.379138115930187</v>
+        <v>10.4247665373611</v>
       </c>
       <c r="D17" t="n">
-        <v>6.369549652722178</v>
+        <v>6.052386239388204</v>
       </c>
       <c r="E17" t="n">
-        <v>16.78106259607594</v>
+        <v>18.09641798770286</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.376997724045335</v>
+        <v>1.848886181499848</v>
       </c>
       <c r="C18" t="n">
-        <v>9.786394910151651</v>
+        <v>12.16962673211895</v>
       </c>
       <c r="D18" t="n">
-        <v>6.87831094801696</v>
+        <v>6.476295080604935</v>
       </c>
       <c r="E18" t="n">
-        <v>19.04170358221395</v>
+        <v>20.49480799422373</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.438749654642459</v>
+        <v>1.855758415429576</v>
       </c>
       <c r="C19" t="n">
-        <v>10.47943024953356</v>
+        <v>13.00557508480807</v>
       </c>
       <c r="D19" t="n">
-        <v>7.04648432975444</v>
+        <v>6.558693165422369</v>
       </c>
       <c r="E19" t="n">
-        <v>19.96466423393046</v>
+        <v>21.42002666566001</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.783588535759152</v>
+        <v>2.069553612983404</v>
       </c>
       <c r="C20" t="n">
-        <v>12.09899980227544</v>
+        <v>14.99699139801047</v>
       </c>
       <c r="D20" t="n">
-        <v>7.533333016290433</v>
+        <v>6.953453917300012</v>
       </c>
       <c r="E20" t="n">
-        <v>22.41592135432502</v>
+        <v>24.01999892829388</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.690756078776814</v>
+        <v>1.231739939656218</v>
       </c>
       <c r="C21" t="n">
-        <v>8.992946415579377</v>
+        <v>11.03015144170785</v>
       </c>
       <c r="D21" t="n">
-        <v>6.317654469075692</v>
+        <v>5.791025365563619</v>
       </c>
       <c r="E21" t="n">
-        <v>17.00135696343188</v>
+        <v>18.05291674692769</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_5_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_5_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.260442742809476</v>
+        <v>1.25930391547255</v>
       </c>
       <c r="C3" t="n">
-        <v>4.606013562446597</v>
+        <v>4.618452305859404</v>
       </c>
       <c r="D3" t="n">
-        <v>6.103314495480647</v>
+        <v>6.07022959784753</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96977080073672</v>
+        <v>11.94798581917948</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.396676421381979</v>
+        <v>1.398810557055675</v>
       </c>
       <c r="C4" t="n">
-        <v>5.062996492293647</v>
+        <v>5.086578033715439</v>
       </c>
       <c r="D4" t="n">
-        <v>6.342292053805713</v>
+        <v>6.297269544460188</v>
       </c>
       <c r="E4" t="n">
-        <v>12.80196496748134</v>
+        <v>12.7826581352313</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.578802158184034</v>
+        <v>1.586349955745567</v>
       </c>
       <c r="C5" t="n">
-        <v>5.671633752341928</v>
+        <v>5.696487010009785</v>
       </c>
       <c r="D5" t="n">
-        <v>6.71079992001698</v>
+        <v>6.563608165707238</v>
       </c>
       <c r="E5" t="n">
-        <v>13.96123583054294</v>
+        <v>13.84644513146259</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.781290504986722</v>
+        <v>1.800573866926601</v>
       </c>
       <c r="C6" t="n">
-        <v>6.415115917972972</v>
+        <v>6.466573648792299</v>
       </c>
       <c r="D6" t="n">
-        <v>7.054469161458062</v>
+        <v>6.968605076605473</v>
       </c>
       <c r="E6" t="n">
-        <v>15.25087558441776</v>
+        <v>15.23575259232437</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.008456258118875</v>
+        <v>2.046044734167766</v>
       </c>
       <c r="C7" t="n">
-        <v>7.335108062210844</v>
+        <v>7.406160467523826</v>
       </c>
       <c r="D7" t="n">
-        <v>7.43124499778359</v>
+        <v>7.355428758007167</v>
       </c>
       <c r="E7" t="n">
-        <v>16.77480931811331</v>
+        <v>16.80763395969876</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.235536555837691</v>
+        <v>1.284380437141434</v>
       </c>
       <c r="C8" t="n">
-        <v>5.086703622820599</v>
+        <v>5.116462564374857</v>
       </c>
       <c r="D8" t="n">
-        <v>5.713769578140964</v>
+        <v>5.691306186061635</v>
       </c>
       <c r="E8" t="n">
-        <v>12.03600975679925</v>
+        <v>12.09214918757793</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.565974206150838</v>
+        <v>1.628184648726347</v>
       </c>
       <c r="C9" t="n">
-        <v>6.338152495282044</v>
+        <v>6.305247260753612</v>
       </c>
       <c r="D9" t="n">
-        <v>6.185634878927182</v>
+        <v>6.360009133208584</v>
       </c>
       <c r="E9" t="n">
-        <v>14.08976158036006</v>
+        <v>14.29344104268854</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.915029934781693</v>
+        <v>2.000441341115657</v>
       </c>
       <c r="C10" t="n">
-        <v>7.798082897987398</v>
+        <v>7.638596794589242</v>
       </c>
       <c r="D10" t="n">
-        <v>6.656282297671239</v>
+        <v>7.054046553588369</v>
       </c>
       <c r="E10" t="n">
-        <v>16.36939513044033</v>
+        <v>16.69308468929327</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.261715931167918</v>
+        <v>2.372459381661122</v>
       </c>
       <c r="C11" t="n">
-        <v>9.377269120524863</v>
+        <v>9.092060433346507</v>
       </c>
       <c r="D11" t="n">
-        <v>7.106183716762858</v>
+        <v>7.666494273405053</v>
       </c>
       <c r="E11" t="n">
-        <v>18.74516876845564</v>
+        <v>19.13101408841268</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.612005334209512</v>
+        <v>2.759062680372665</v>
       </c>
       <c r="C12" t="n">
-        <v>11.02054820044896</v>
+        <v>10.5710824796089</v>
       </c>
       <c r="D12" t="n">
-        <v>7.556019716006806</v>
+        <v>8.250345296180567</v>
       </c>
       <c r="E12" t="n">
-        <v>21.18857325066528</v>
+        <v>21.58049045616213</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.943727208531993</v>
+        <v>3.125312210611032</v>
       </c>
       <c r="C13" t="n">
-        <v>12.69204295887494</v>
+        <v>12.06729175524794</v>
       </c>
       <c r="D13" t="n">
-        <v>8.00301768980259</v>
+        <v>8.845763492688986</v>
       </c>
       <c r="E13" t="n">
-        <v>23.63878785720952</v>
+        <v>24.03836745854796</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.688399884286622</v>
+        <v>1.787752751956399</v>
       </c>
       <c r="C14" t="n">
-        <v>8.787015017136568</v>
+        <v>8.418388389145974</v>
       </c>
       <c r="D14" t="n">
-        <v>6.048174541736985</v>
+        <v>6.764084602627843</v>
       </c>
       <c r="E14" t="n">
-        <v>16.52358944316017</v>
+        <v>16.97022574373022</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.732401816390964</v>
+        <v>1.848198958106876</v>
       </c>
       <c r="C15" t="n">
-        <v>9.53579399116561</v>
+        <v>9.02035681148195</v>
       </c>
       <c r="D15" t="n">
-        <v>6.043471970233643</v>
+        <v>6.864615567542717</v>
       </c>
       <c r="E15" t="n">
-        <v>17.31166777779022</v>
+        <v>17.73317133713154</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.014477566775157</v>
+        <v>2.164233361580966</v>
       </c>
       <c r="C16" t="n">
-        <v>11.28315764256929</v>
+        <v>10.55915798059544</v>
       </c>
       <c r="D16" t="n">
-        <v>6.535170490428616</v>
+        <v>7.447704981526027</v>
       </c>
       <c r="E16" t="n">
-        <v>19.83280569977307</v>
+        <v>20.17109632370244</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.619265210953562</v>
+        <v>1.752134945246325</v>
       </c>
       <c r="C17" t="n">
-        <v>10.4247665373611</v>
+        <v>9.65998507575283</v>
       </c>
       <c r="D17" t="n">
-        <v>6.052386239388204</v>
+        <v>6.981580989026683</v>
       </c>
       <c r="E17" t="n">
-        <v>18.09641798770286</v>
+        <v>18.39370101002584</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.848886181499848</v>
+        <v>2.011483236277205</v>
       </c>
       <c r="C18" t="n">
-        <v>12.16962673211895</v>
+        <v>11.1679200970448</v>
       </c>
       <c r="D18" t="n">
-        <v>6.476295080604935</v>
+        <v>7.474477241420836</v>
       </c>
       <c r="E18" t="n">
-        <v>20.49480799422373</v>
+        <v>20.65388057474285</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.855758415429576</v>
+        <v>2.034161608245306</v>
       </c>
       <c r="C19" t="n">
-        <v>13.00557508480807</v>
+        <v>11.83752111872634</v>
       </c>
       <c r="D19" t="n">
-        <v>6.558693165422369</v>
+        <v>7.618460359725673</v>
       </c>
       <c r="E19" t="n">
-        <v>21.42002666566001</v>
+        <v>21.49014308669732</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.069553612983404</v>
+        <v>2.287747040252258</v>
       </c>
       <c r="C20" t="n">
-        <v>14.99699139801047</v>
+        <v>13.55849539183987</v>
       </c>
       <c r="D20" t="n">
-        <v>6.953453917300012</v>
+        <v>8.123157219524874</v>
       </c>
       <c r="E20" t="n">
-        <v>24.01999892829388</v>
+        <v>23.969399651617</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.231739939656218</v>
+        <v>1.368379585133289</v>
       </c>
       <c r="C21" t="n">
-        <v>11.03015144170785</v>
+        <v>9.92946500309154</v>
       </c>
       <c r="D21" t="n">
-        <v>5.791025365563619</v>
+        <v>6.824550443732405</v>
       </c>
       <c r="E21" t="n">
-        <v>18.05291674692769</v>
+        <v>18.12239503195723</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_5_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_5_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.25930391547255</v>
+        <v>2.590075767658592</v>
       </c>
       <c r="C3" t="n">
-        <v>4.618452305859404</v>
+        <v>7.788663128567448</v>
       </c>
       <c r="D3" t="n">
-        <v>6.07022959784753</v>
+        <v>8.227023931691608</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94798581917948</v>
+        <v>18.60576282791765</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.398810557055675</v>
+        <v>1.081226398039968</v>
       </c>
       <c r="C4" t="n">
-        <v>5.086578033715439</v>
+        <v>4.654337501578063</v>
       </c>
       <c r="D4" t="n">
-        <v>6.297269544460188</v>
+        <v>5.769131617188566</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7826581352313</v>
+        <v>11.5046955168066</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.586349955745567</v>
+        <v>1.188125455709738</v>
       </c>
       <c r="C5" t="n">
-        <v>5.696487010009785</v>
+        <v>5.451811779461792</v>
       </c>
       <c r="D5" t="n">
-        <v>6.563608165707238</v>
+        <v>6.053503081519351</v>
       </c>
       <c r="E5" t="n">
-        <v>13.84644513146259</v>
+        <v>12.69344031669088</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.800573866926601</v>
+        <v>1.309970836531896</v>
       </c>
       <c r="C6" t="n">
-        <v>6.466573648792299</v>
+        <v>6.521089269203065</v>
       </c>
       <c r="D6" t="n">
-        <v>6.968605076605473</v>
+        <v>6.362498305013554</v>
       </c>
       <c r="E6" t="n">
-        <v>15.23575259232437</v>
+        <v>14.19355841074851</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.046044734167766</v>
+        <v>1.434305694881262</v>
       </c>
       <c r="C7" t="n">
-        <v>7.406160467523826</v>
+        <v>7.83304262401876</v>
       </c>
       <c r="D7" t="n">
-        <v>7.355428758007167</v>
+        <v>6.701928974061455</v>
       </c>
       <c r="E7" t="n">
-        <v>16.80763395969876</v>
+        <v>15.96927729296148</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.284380437141434</v>
+        <v>1.566952226530762</v>
       </c>
       <c r="C8" t="n">
-        <v>5.116462564374857</v>
+        <v>9.328094491748187</v>
       </c>
       <c r="D8" t="n">
-        <v>5.691306186061635</v>
+        <v>7.064323773224732</v>
       </c>
       <c r="E8" t="n">
-        <v>12.09214918757793</v>
+        <v>17.95937049150368</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.628184648726347</v>
+        <v>1.686410875038602</v>
       </c>
       <c r="C9" t="n">
-        <v>6.305247260753612</v>
+        <v>10.97591202566401</v>
       </c>
       <c r="D9" t="n">
-        <v>6.360009133208584</v>
+        <v>7.421412014340663</v>
       </c>
       <c r="E9" t="n">
-        <v>14.29344104268854</v>
+        <v>20.08373491504327</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.000441341115657</v>
+        <v>1.049458843408713</v>
       </c>
       <c r="C10" t="n">
-        <v>7.638596794589242</v>
+        <v>7.935005272005971</v>
       </c>
       <c r="D10" t="n">
-        <v>7.054046553588369</v>
+        <v>5.820340352012428</v>
       </c>
       <c r="E10" t="n">
-        <v>16.69308468929327</v>
+        <v>14.80480446742711</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.372459381661122</v>
+        <v>0.9839370016272807</v>
       </c>
       <c r="C11" t="n">
-        <v>9.092060433346507</v>
+        <v>8.68754433974228</v>
       </c>
       <c r="D11" t="n">
-        <v>7.666494273405053</v>
+        <v>5.645245648960009</v>
       </c>
       <c r="E11" t="n">
-        <v>19.13101408841268</v>
+        <v>15.31672699032957</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.759062680372665</v>
+        <v>1.058903256323567</v>
       </c>
       <c r="C12" t="n">
-        <v>10.5710824796089</v>
+        <v>10.38487812813755</v>
       </c>
       <c r="D12" t="n">
-        <v>8.250345296180567</v>
+        <v>5.967239260998878</v>
       </c>
       <c r="E12" t="n">
-        <v>21.58049045616213</v>
+        <v>17.41102064545999</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.125312210611032</v>
+        <v>0.8349273350767</v>
       </c>
       <c r="C13" t="n">
-        <v>12.06729175524794</v>
+        <v>9.891638264046909</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845763492688986</v>
+        <v>5.399416023816608</v>
       </c>
       <c r="E13" t="n">
-        <v>24.03836745854796</v>
+        <v>16.12598162294022</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.787752751956399</v>
+        <v>0.9003313671336226</v>
       </c>
       <c r="C14" t="n">
-        <v>8.418388389145974</v>
+        <v>11.56938618574245</v>
       </c>
       <c r="D14" t="n">
-        <v>6.764084602627843</v>
+        <v>5.689159223770969</v>
       </c>
       <c r="E14" t="n">
-        <v>16.97022574373022</v>
+        <v>18.15887677664704</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.848198958106876</v>
+        <v>0.8728817013228818</v>
       </c>
       <c r="C15" t="n">
-        <v>9.02035681148195</v>
+        <v>12.44469280389482</v>
       </c>
       <c r="D15" t="n">
-        <v>6.864615567542717</v>
+        <v>5.687077918637966</v>
       </c>
       <c r="E15" t="n">
-        <v>17.73317133713154</v>
+        <v>19.00465242385567</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.164233361580966</v>
+        <v>0.9498016339506192</v>
       </c>
       <c r="C16" t="n">
-        <v>10.55915798059544</v>
+        <v>14.44732067587972</v>
       </c>
       <c r="D16" t="n">
-        <v>7.447704981526027</v>
+        <v>6.095111899477025</v>
       </c>
       <c r="E16" t="n">
-        <v>20.17109632370244</v>
+        <v>21.49223420930737</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.752134945246325</v>
+        <v>0.5650350737022093</v>
       </c>
       <c r="C17" t="n">
-        <v>9.65998507575283</v>
+        <v>10.67888211312834</v>
       </c>
       <c r="D17" t="n">
-        <v>6.981580989026683</v>
+        <v>5.040921032133842</v>
       </c>
       <c r="E17" t="n">
-        <v>18.39370101002584</v>
+        <v>16.28483821896439</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.011483236277205</v>
+        <v>0.4470780870369551</v>
       </c>
       <c r="C18" t="n">
-        <v>11.1679200970448</v>
+        <v>9.548429084119267</v>
       </c>
       <c r="D18" t="n">
-        <v>7.474477241420836</v>
+        <v>4.552040127850059</v>
       </c>
       <c r="E18" t="n">
-        <v>20.65388057474285</v>
+        <v>14.54754729900628</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.034161608245306</v>
+        <v>0.5202968308196821</v>
       </c>
       <c r="C19" t="n">
-        <v>11.83752111872634</v>
+        <v>11.82824360292121</v>
       </c>
       <c r="D19" t="n">
-        <v>7.618460359725673</v>
+        <v>4.987229250188585</v>
       </c>
       <c r="E19" t="n">
-        <v>21.49014308669732</v>
+        <v>17.33576968392947</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.287747040252258</v>
+        <v>0.5885577486959629</v>
       </c>
       <c r="C20" t="n">
-        <v>13.55849539183987</v>
+        <v>14.21691430717004</v>
       </c>
       <c r="D20" t="n">
-        <v>8.123157219524874</v>
+        <v>5.484808439131996</v>
       </c>
       <c r="E20" t="n">
-        <v>23.969399651617</v>
+        <v>20.290280494998</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.368379585133289</v>
+        <v>0.6444388280216913</v>
       </c>
       <c r="C21" t="n">
-        <v>9.92946500309154</v>
+        <v>16.7304731368761</v>
       </c>
       <c r="D21" t="n">
-        <v>6.824550443732405</v>
+        <v>5.883447094441412</v>
       </c>
       <c r="E21" t="n">
-        <v>18.12239503195723</v>
+        <v>23.25835905933921</v>
       </c>
     </row>
   </sheetData>
